--- a/Dashboards/data/Data final/pobreza/pobreza_educacion.xlsx
+++ b/Dashboards/data/Data final/pobreza/pobreza_educacion.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="180" uniqueCount="8">
   <si>
     <t>anio</t>
   </si>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -163,7 +163,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>57.847000122070312</v>
+        <v>57.847000122070313</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -177,7 +177,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="1">
-        <v>32.615798950195312</v>
+        <v>32.615798950195313</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -191,7 +191,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="1">
-        <v>18.131200790405273</v>
+        <v>18.131200790405274</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -443,7 +443,7 @@
         <v>2</v>
       </c>
       <c r="C26" s="1">
-        <v>35.801101684570312</v>
+        <v>35.801101684570313</v>
       </c>
       <c r="D26" t="s">
         <v>6</v>
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="C48" s="1">
-        <v>4.2248001098632812</v>
+        <v>4.2248001098632813</v>
       </c>
       <c r="D48" t="s">
         <v>6</v>
@@ -1171,7 +1171,7 @@
         <v>2</v>
       </c>
       <c r="C78" s="1">
-        <v>28.071599960327148</v>
+        <v>28.071599960327149</v>
       </c>
       <c r="D78" t="s">
         <v>6</v>
